--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_atacama.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -621,7 +621,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3302</v>
+        <v>3202</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -634,7 +634,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3202</v>
+        <v>3302</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:19</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
